--- a/data/trans_dic/P15A-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P15A-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,12</t>
+          <t>1,69; 6,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 7,05</t>
+          <t>2,25; 6,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,52</t>
+          <t>0,68; 4,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,83</t>
+          <t>1,2; 4,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,92</t>
+          <t>1,09; 5,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,08</t>
+          <t>0,95; 5,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,95</t>
+          <t>1,36; 5,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,28</t>
+          <t>2,84; 6,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,05</t>
+          <t>1,78; 4,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,28</t>
+          <t>1,93; 5,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,4</t>
+          <t>1,44; 4,29</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,68</t>
+          <t>2,45; 4,77</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,11</t>
+          <t>0,63; 3,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,77</t>
+          <t>1,14; 3,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,64</t>
+          <t>0,41; 2,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,85</t>
+          <t>1,07; 4,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,16</t>
+          <t>0,91; 3,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,7</t>
+          <t>0,6; 2,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,05</t>
+          <t>0,19; 1,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,67</t>
+          <t>2,06; 4,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,71</t>
+          <t>0,99; 2,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,98</t>
+          <t>1,06; 2,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,75</t>
+          <t>0,59; 1,89</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,04</t>
+          <t>1,86; 4,23</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 9,13</t>
+          <t>3,37; 9,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,43</t>
+          <t>2,83; 7,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 6,51</t>
+          <t>2,07; 6,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,68</t>
+          <t>0,71; 3,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,09</t>
+          <t>0,34; 3,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 8,05</t>
+          <t>2,94; 8,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,45</t>
+          <t>0,79; 3,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,09</t>
+          <t>1,59; 4,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,21</t>
+          <t>2,11; 5,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,89</t>
+          <t>3,34; 6,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,27</t>
+          <t>1,76; 4,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,33</t>
+          <t>1,46; 3,37</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 7,51</t>
+          <t>3,1; 7,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,54</t>
+          <t>1,99; 6,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 7,12</t>
+          <t>2,69; 7,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 6,81</t>
+          <t>0,57; 6,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,81</t>
+          <t>1,37; 4,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,44</t>
+          <t>0,78; 3,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 7,74</t>
+          <t>2,85; 7,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,41</t>
+          <t>0,55; 4,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,24</t>
+          <t>2,64; 5,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,3</t>
+          <t>1,76; 4,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,7</t>
+          <t>3,27; 6,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,78</t>
+          <t>0,72; 3,9</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,89</t>
+          <t>1,41; 7,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 6,38</t>
+          <t>1,43; 6,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,38</t>
+          <t>0,93; 5,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,36</t>
+          <t>0,3; 3,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 7,63</t>
+          <t>1,47; 7,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,5</t>
+          <t>1,9; 7,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,12</t>
+          <t>0,49; 4,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,87</t>
+          <t>2,16; 5,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,05</t>
+          <t>2,3; 6,02</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,06</t>
+          <t>1,09; 3,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,64</t>
+          <t>0,14; 1,76</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,45</t>
+          <t>1,5; 6,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,65</t>
+          <t>1,05; 5,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,36; 9,2</t>
+          <t>3,18; 8,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,68</t>
+          <t>2,05; 6,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,58</t>
+          <t>1,89; 6,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,67; 9,32</t>
+          <t>3,32; 9,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,17; 13,47</t>
+          <t>6,38; 13,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,75</t>
+          <t>3,57; 7,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,53</t>
+          <t>2,12; 5,63</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,44</t>
+          <t>2,81; 6,51</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,54; 10,24</t>
+          <t>5,48; 10,29</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,21</t>
+          <t>3,28; 5,95</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,41</t>
+          <t>2,88; 6,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,06</t>
+          <t>2,35; 5,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,55</t>
+          <t>0,5; 2,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,47</t>
+          <t>1,15; 3,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,52</t>
+          <t>1,7; 4,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,35</t>
+          <t>1,72; 4,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,83</t>
+          <t>0,3; 1,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,6</t>
+          <t>1,01; 3,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,9</t>
+          <t>2,71; 4,89</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,28</t>
+          <t>2,16; 4,14</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,77</t>
+          <t>0,54; 1,77</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,09</t>
+          <t>1,3; 3,2</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,24</t>
+          <t>2,34; 5,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,32</t>
+          <t>0,52; 2,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,55</t>
+          <t>1,47; 3,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,01</t>
+          <t>0,62; 2,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,01</t>
+          <t>2,34; 4,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,97</t>
+          <t>0,94; 2,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,01</t>
+          <t>1,0; 3,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,95</t>
+          <t>1,18; 2,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,57</t>
+          <t>2,69; 4,63</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,25</t>
+          <t>0,89; 2,22</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,89</t>
+          <t>1,46; 2,93</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,55</t>
+          <t>0,95; 2,58</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,42</t>
+          <t>3,15; 4,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,56</t>
+          <t>2,34; 3,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,19</t>
+          <t>2,09; 3,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,82</t>
+          <t>1,52; 2,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,4</t>
+          <t>2,23; 3,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,38</t>
+          <t>2,21; 3,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,11</t>
+          <t>1,95; 3,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,13</t>
+          <t>1,96; 3,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,85; 3,77</t>
+          <t>2,87; 3,75</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,24</t>
+          <t>2,43; 3,27</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,17; 2,97</t>
+          <t>2,2; 2,97</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,89; 2,71</t>
+          <t>1,88; 2,69</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4616; 16720</t>
+          <t>4624; 16423</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6911; 20791</t>
+          <t>6638; 19691</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2607; 13270</t>
+          <t>2009; 12512</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3866; 15035</t>
+          <t>3737; 14570</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2882; 15445</t>
+          <t>2845; 14174</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2859; 14588</t>
+          <t>2739; 14800</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4404; 17171</t>
+          <t>3930; 16723</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8392; 18184</t>
+          <t>8221; 18267</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9291; 26959</t>
+          <t>9501; 26487</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12083; 30735</t>
+          <t>11231; 29075</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8778; 25622</t>
+          <t>8401; 24999</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14517; 28116</t>
+          <t>14734; 28673</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3084; 15327</t>
+          <t>3106; 15564</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4973; 19060</t>
+          <t>5764; 19012</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2095; 13274</t>
+          <t>2085; 12563</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5284; 25136</t>
+          <t>5567; 24197</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4059; 15914</t>
+          <t>4589; 16932</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3120; 14117</t>
+          <t>3145; 14681</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1269; 10737</t>
+          <t>1009; 9838</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10388; 24049</t>
+          <t>10606; 23617</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9656; 27025</t>
+          <t>9887; 26773</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10949; 30628</t>
+          <t>10950; 29374</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5139; 17921</t>
+          <t>6086; 19431</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17876; 41699</t>
+          <t>19248; 43705</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10818; 29102</t>
+          <t>10759; 29405</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8616; 24080</t>
+          <t>9185; 23240</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6907; 20725</t>
+          <t>6595; 20808</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2625; 11646</t>
+          <t>2259; 11024</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1140; 10362</t>
+          <t>1124; 11207</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10049; 27441</t>
+          <t>10009; 28574</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1915; 11605</t>
+          <t>2662; 12317</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5148; 14294</t>
+          <t>5547; 14632</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13782; 34056</t>
+          <t>13831; 32973</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22666; 45825</t>
+          <t>22204; 46069</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11193; 27934</t>
+          <t>11509; 27559</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9600; 22143</t>
+          <t>9693; 22419</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10788; 26949</t>
+          <t>11112; 26832</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7682; 24471</t>
+          <t>7445; 25505</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9307; 26359</t>
+          <t>9950; 27067</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1802; 21286</t>
+          <t>1783; 20761</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5316; 17882</t>
+          <t>5078; 17537</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2863; 13377</t>
+          <t>3032; 13985</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10638; 29983</t>
+          <t>11038; 30545</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2418; 20988</t>
+          <t>2626; 19233</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18827; 38280</t>
+          <t>19240; 40222</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12356; 32842</t>
+          <t>13419; 33344</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25330; 50726</t>
+          <t>24748; 51815</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5265; 29782</t>
+          <t>5710; 30778</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3094; 14002</t>
+          <t>2868; 14429</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2892; 13562</t>
+          <t>3051; 14408</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1938; 11360</t>
+          <t>1957; 11962</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>524; 6006</t>
+          <t>535; 6181</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3106; 15837</t>
+          <t>3054; 16254</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4178; 16466</t>
+          <t>4177; 16097</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1055; 8999</t>
+          <t>1060; 9958</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2969</t>
+          <t>0; 3262</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8986; 24112</t>
+          <t>8893; 24587</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9703; 26146</t>
+          <t>9928; 26037</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4106; 17464</t>
+          <t>4672; 16480</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>546; 6352</t>
+          <t>549; 6806</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3809; 17464</t>
+          <t>4055; 18199</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2808; 15471</t>
+          <t>2873; 15896</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8845; 24209</t>
+          <t>8373; 23145</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6078; 18005</t>
+          <t>5527; 17354</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5237; 18298</t>
+          <t>5245; 18783</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10267; 26088</t>
+          <t>9295; 26476</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16864; 36785</t>
+          <t>17434; 36821</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9432; 19923</t>
+          <t>9168; 19458</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12135; 30383</t>
+          <t>11660; 30924</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15282; 35678</t>
+          <t>15588; 36068</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29683; 54890</t>
+          <t>29399; 55153</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17457; 32706</t>
+          <t>17281; 31344</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>17770; 39449</t>
+          <t>17697; 38426</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13628; 33533</t>
+          <t>15560; 35299</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3176; 16740</t>
+          <t>3272; 16958</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7060; 21675</t>
+          <t>7165; 21390</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11150; 28876</t>
+          <t>10861; 27410</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12052; 30180</t>
+          <t>11937; 29905</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1847; 12678</t>
+          <t>2056; 13748</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8800; 30580</t>
+          <t>8613; 32320</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>33284; 61413</t>
+          <t>33969; 61287</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31097; 58022</t>
+          <t>29331; 56145</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7036; 23831</t>
+          <t>7324; 23915</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>19392; 45578</t>
+          <t>19132; 47139</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>17245; 38942</t>
+          <t>17397; 38611</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4012; 18038</t>
+          <t>4035; 17926</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10746; 27643</t>
+          <t>11454; 27745</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5437; 27946</t>
+          <t>5786; 26997</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>18372; 39231</t>
+          <t>18332; 38416</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8209; 24429</t>
+          <t>7776; 24175</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8617; 24850</t>
+          <t>8257; 24896</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>8020; 21142</t>
+          <t>8468; 21481</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>40046; 69790</t>
+          <t>41113; 70732</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14809; 36002</t>
+          <t>14264; 35589</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>22193; 46393</t>
+          <t>23469; 46982</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>16604; 42061</t>
+          <t>15658; 42438</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>102111; 144855</t>
+          <t>103130; 147090</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>80016; 122151</t>
+          <t>80175; 120595</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>72684; 108185</t>
+          <t>71065; 108483</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>54522; 97424</t>
+          <t>52714; 97446</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>75288; 115059</t>
+          <t>75267; 116065</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>79889; 120306</t>
+          <t>78736; 119152</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>71030; 110136</t>
+          <t>69056; 107560</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>73012; 114774</t>
+          <t>71915; 111038</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>189848; 251213</t>
+          <t>190759; 249424</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>167014; 226559</t>
+          <t>169870; 228695</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>150790; 205997</t>
+          <t>152738; 206076</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>134783; 193208</t>
+          <t>133759; 191295</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15A-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P15A-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,02</t>
+          <t>1,72; 6,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,68</t>
+          <t>2,24; 6,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,26</t>
+          <t>0,79; 4,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,68</t>
+          <t>1,39; 4,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,43</t>
+          <t>1,1; 6,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,15</t>
+          <t>0,86; 5,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,79</t>
+          <t>1,47; 6,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 6,31</t>
+          <t>2,79; 6,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,96</t>
+          <t>1,88; 5,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,0</t>
+          <t>2,1; 5,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,29</t>
+          <t>1,55; 4,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,77</t>
+          <t>2,39; 4,68</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,16</t>
+          <t>0,62; 3,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,76</t>
+          <t>1,14; 3,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,5</t>
+          <t>0,42; 2,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,67</t>
+          <t>1,06; 4,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,36</t>
+          <t>0,79; 3,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,8</t>
+          <t>0,6; 2,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,88</t>
+          <t>0,21; 2,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,59</t>
+          <t>1,99; 4,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,69</t>
+          <t>1,02; 2,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,85</t>
+          <t>0,99; 2,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,89</t>
+          <t>0,5; 1,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,23</t>
+          <t>1,77; 3,91</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 9,22</t>
+          <t>3,65; 9,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 7,17</t>
+          <t>2,84; 7,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,53</t>
+          <t>2,22; 6,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,49</t>
+          <t>1,0; 4,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,34</t>
+          <t>0,34; 3,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 8,38</t>
+          <t>2,91; 7,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,66</t>
+          <t>0,63; 3,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,19</t>
+          <t>1,54; 4,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,04</t>
+          <t>2,22; 5,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,93</t>
+          <t>3,47; 6,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,21</t>
+          <t>1,73; 4,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,37</t>
+          <t>1,54; 3,53</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 7,48</t>
+          <t>3,26; 7,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,82</t>
+          <t>1,92; 6,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,32</t>
+          <t>2,73; 7,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,64</t>
+          <t>0,93; 6,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,72</t>
+          <t>1,21; 4,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,6</t>
+          <t>0,74; 3,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 7,89</t>
+          <t>2,81; 7,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,04</t>
+          <t>0,69; 5,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,51</t>
+          <t>2,55; 5,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,37</t>
+          <t>1,76; 4,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,84</t>
+          <t>3,2; 6,5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,9</t>
+          <t>1,01; 4,35</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 7,1</t>
+          <t>1,47; 7,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 6,78</t>
+          <t>1,5; 6,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,66</t>
+          <t>0,92; 5,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,46</t>
+          <t>0,25; 3,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 7,83</t>
+          <t>1,46; 7,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,33</t>
+          <t>2,2; 7,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,56</t>
+          <t>0,48; 4,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,98</t>
+          <t>1,93; 5,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,02</t>
+          <t>2,27; 6,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,83</t>
+          <t>1,06; 4,34</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,76</t>
+          <t>0,21; 1,73</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,72</t>
+          <t>1,44; 6,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,8</t>
+          <t>0,99; 5,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,18; 8,8</t>
+          <t>3,46; 9,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,44</t>
+          <t>2,01; 5,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,75</t>
+          <t>2,0; 6,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,32; 9,45</t>
+          <t>3,69; 10,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,38; 13,48</t>
+          <t>6,01; 13,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,57; 7,57</t>
+          <t>3,65; 7,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,63</t>
+          <t>2,07; 5,23</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,51</t>
+          <t>2,74; 6,46</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,48; 10,29</t>
+          <t>5,54; 10,53</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,95</t>
+          <t>3,23; 5,94</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,25</t>
+          <t>2,78; 6,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,35; 5,33</t>
+          <t>2,28; 5,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,58</t>
+          <t>0,48; 2,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,43</t>
+          <t>1,31; 3,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,29</t>
+          <t>1,71; 4,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,31</t>
+          <t>1,74; 4,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,99</t>
+          <t>0,28; 1,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,81</t>
+          <t>2,06; 4,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,89</t>
+          <t>2,67; 4,87</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,14</t>
+          <t>2,25; 4,18</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,77</t>
+          <t>0,58; 1,81</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,2</t>
+          <t>1,93; 3,6</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,19</t>
+          <t>2,34; 5,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,3</t>
+          <t>0,53; 2,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,56</t>
+          <t>1,42; 3,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,91</t>
+          <t>1,24; 3,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,9</t>
+          <t>2,26; 4,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,93</t>
+          <t>0,91; 2,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,01</t>
+          <t>1,01; 2,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,99</t>
+          <t>1,1; 2,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,63</t>
+          <t>2,66; 4,59</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,22</t>
+          <t>0,89; 2,16</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,93</t>
+          <t>1,48; 2,89</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,58</t>
+          <t>1,37; 2,81</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,27 +1804,27 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>2,5%</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,49</t>
+          <t>3,14; 4,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,52</t>
+          <t>2,3; 3,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,2</t>
+          <t>2,09; 3,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,82</t>
+          <t>1,84; 3,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,43</t>
+          <t>2,25; 3,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,35</t>
+          <t>2,26; 3,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,03</t>
+          <t>1,97; 3,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,03</t>
+          <t>2,22; 3,2</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,87; 3,75</t>
+          <t>2,86; 3,72</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,27</t>
+          <t>2,41; 3,25</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,2; 2,97</t>
+          <t>2,2; 2,96</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,88; 2,69</t>
+          <t>2,15; 2,92</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12374</t>
+          <t>13265</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>21975</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4624; 16423</t>
+          <t>4700; 16442</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6638; 19691</t>
+          <t>6588; 20569</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2009; 12512</t>
+          <t>2331; 12760</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3737; 14570</t>
+          <t>4430; 15403</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2845; 14174</t>
+          <t>2874; 15784</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2739; 14800</t>
+          <t>2481; 15449</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3930; 16723</t>
+          <t>4242; 17849</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8221; 18267</t>
+          <t>8809; 19025</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9501; 26487</t>
+          <t>10020; 26945</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11231; 29075</t>
+          <t>12211; 29755</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8401; 24999</t>
+          <t>9024; 25243</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14734; 28673</t>
+          <t>15187; 29697</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16114</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27912</t>
+          <t>28466</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3106; 15564</t>
+          <t>3047; 15694</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5764; 19012</t>
+          <t>5771; 19781</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2085; 12563</t>
+          <t>2110; 12559</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5567; 24197</t>
+          <t>5615; 23705</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4589; 16932</t>
+          <t>4006; 15932</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3145; 14681</t>
+          <t>3127; 14755</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1009; 9838</t>
+          <t>1086; 11112</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10606; 23617</t>
+          <t>10859; 24919</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9887; 26773</t>
+          <t>10170; 27231</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10950; 29374</t>
+          <t>10174; 27965</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6086; 19431</t>
+          <t>5162; 18754</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19248; 43705</t>
+          <t>19012; 42132</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9048</t>
+          <t>9071</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14814</t>
+          <t>15977</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10759; 29405</t>
+          <t>11630; 28777</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9185; 23240</t>
+          <t>9206; 24311</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6595; 20808</t>
+          <t>7062; 20382</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2259; 11024</t>
+          <t>3157; 13574</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1124; 11207</t>
+          <t>1133; 10091</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10009; 28574</t>
+          <t>9940; 26972</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2662; 12317</t>
+          <t>2116; 11887</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5547; 14632</t>
+          <t>5471; 14626</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13831; 32973</t>
+          <t>14555; 36362</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22204; 46069</t>
+          <t>23080; 45755</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11509; 27559</t>
+          <t>11308; 27854</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9693; 22419</t>
+          <t>10370; 23737</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6773</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14013</t>
+          <t>17581</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11112; 26832</t>
+          <t>11681; 28038</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7445; 25505</t>
+          <t>7179; 23781</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9950; 27067</t>
+          <t>10091; 27778</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1783; 20761</t>
+          <t>3453; 25374</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5078; 17537</t>
+          <t>4510; 17827</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3032; 13985</t>
+          <t>2888; 14686</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11038; 30545</t>
+          <t>10894; 30463</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2626; 19233</t>
+          <t>2908; 21597</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19240; 40222</t>
+          <t>18643; 38278</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13419; 33344</t>
+          <t>13411; 32408</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24748; 51815</t>
+          <t>24234; 49221</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5710; 30778</t>
+          <t>8061; 34552</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2953</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2868; 14429</t>
+          <t>2984; 15016</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3051; 14408</t>
+          <t>3186; 14708</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1957; 11962</t>
+          <t>1936; 11291</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>535; 6181</t>
+          <t>521; 7347</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3054; 16254</t>
+          <t>3031; 16590</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4177; 16097</t>
+          <t>4827; 17285</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1060; 9958</t>
+          <t>1054; 9101</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3262</t>
+          <t>0; 2897</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8893; 24587</t>
+          <t>7929; 24084</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9928; 26037</t>
+          <t>9823; 26909</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4672; 16480</t>
+          <t>4569; 18642</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>549; 6806</t>
+          <t>895; 7507</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9652</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>23169</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4055; 18199</t>
+          <t>3910; 17472</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2873; 15896</t>
+          <t>2715; 14734</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8373; 23145</t>
+          <t>9110; 24316</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5527; 17354</t>
+          <t>5438; 15832</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5245; 18783</t>
+          <t>5553; 19261</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9295; 26476</t>
+          <t>10327; 29494</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17434; 36821</t>
+          <t>16420; 36145</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9168; 19458</t>
+          <t>9633; 20233</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11660; 30924</t>
+          <t>11389; 28715</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15588; 36068</t>
+          <t>15197; 35801</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29399; 55153</t>
+          <t>29715; 56450</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17281; 31344</t>
+          <t>17237; 31749</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>15960</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>19933</t>
+          <t>23281</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>33047</t>
+          <t>39241</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>17697; 38426</t>
+          <t>17107; 39125</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15560; 35299</t>
+          <t>15102; 34720</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3272; 16958</t>
+          <t>3183; 16091</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7165; 21390</t>
+          <t>9424; 26452</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10861; 27410</t>
+          <t>10938; 27531</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11937; 29905</t>
+          <t>12063; 29410</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2056; 13748</t>
+          <t>1961; 13086</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8613; 32320</t>
+          <t>15940; 33474</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>33969; 61287</t>
+          <t>33449; 61016</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29331; 56145</t>
+          <t>30572; 56753</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7324; 23915</t>
+          <t>7884; 24396</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>19132; 47139</t>
+          <t>28770; 53764</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15250</t>
+          <t>17045</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>15374</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>28473</t>
+          <t>32418</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>17397; 38611</t>
+          <t>17394; 38292</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4035; 17926</t>
+          <t>4166; 18671</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11454; 27745</t>
+          <t>11047; 28290</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5786; 26997</t>
+          <t>9883; 30930</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>18332; 38416</t>
+          <t>17723; 38765</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7776; 24175</t>
+          <t>7498; 23564</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8257; 24896</t>
+          <t>8327; 24596</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>8468; 21481</t>
+          <t>9162; 24676</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>41113; 70732</t>
+          <t>40589; 70043</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14264; 35589</t>
+          <t>14187; 34569</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>23469; 46982</t>
+          <t>23711; 46374</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>15658; 42438</t>
+          <t>22288; 45831</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>72930</t>
+          <t>82343</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>91486</t>
+          <t>99438</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>164416</t>
+          <t>181781</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>103130; 147090</t>
+          <t>102848; 146963</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>80175; 120595</t>
+          <t>78985; 119930</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>71065; 108483</t>
+          <t>70895; 108804</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>52714; 97446</t>
+          <t>65126; 107011</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>75267; 116065</t>
+          <t>75895; 113942</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>78736; 119152</t>
+          <t>80274; 120256</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>69056; 107560</t>
+          <t>69712; 110150</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>71915; 111038</t>
+          <t>82827; 119612</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>190759; 249424</t>
+          <t>190398; 247827</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>169870; 228695</t>
+          <t>168303; 227313</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>152738; 206076</t>
+          <t>152632; 205724</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>133759; 191295</t>
+          <t>156515; 211970</t>
         </is>
       </c>
     </row>
